--- a/public/document/Keanggotaan Tim Template.xlsx
+++ b/public/document/Keanggotaan Tim Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rifqind\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xampp\htdocs\singkat\public\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F452126-3584-46B5-8E0C-2489107A88EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E3327A-1608-499C-8567-6471C599D89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4C485BC0-E57A-4123-BC42-163A0E71FB7D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{4C485BC0-E57A-4123-BC42-163A0E71FB7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,16 +44,10 @@
     <t>nama_tim</t>
   </si>
   <si>
-    <t>nama_pegawai</t>
-  </si>
-  <si>
     <t>keanggotaan_tim</t>
   </si>
   <si>
     <t>(nama tim harus sesuai dengan yang ada di sistem)</t>
-  </si>
-  <si>
-    <t>(nama pegawai harus sesuai dengan yang ada di sistem)</t>
   </si>
   <si>
     <r>
@@ -80,6 +74,12 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>(nip pegawai harus sesuai dengan yang ada di sistem)</t>
+  </si>
+  <si>
+    <t>nip_bps</t>
   </si>
 </sst>
 </file>
@@ -480,21 +480,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
